--- a/artfynd/A 45428-2020 artfynd.xlsx
+++ b/artfynd/A 45428-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45428-2020 artfynd.xlsx
+++ b/artfynd/A 45428-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89318713</v>
+        <v>98052071</v>
       </c>
       <c r="B4" t="n">
         <v>96334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -933,19 +933,23 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sovtjärnen, SV om, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361011.4931558943</v>
+        <v>360999.5228702108</v>
       </c>
       <c r="R4" t="n">
-        <v>6599461.099589986</v>
+        <v>6599453.921583855</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,14 +971,9 @@
           <t>Glava</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>S-Arv-0783</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -984,7 +983,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -998,32 +997,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jan Rees, Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98052071</v>
+        <v>98052082</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>90008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,31 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1137,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98052082</v>
+        <v>98052068</v>
       </c>
       <c r="B6" t="n">
-        <v>90008</v>
+        <v>56401</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1152,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,12 +1178,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360999.5228702108</v>
+        <v>360901.2848806324</v>
       </c>
       <c r="R6" t="n">
-        <v>6599453.921583855</v>
+        <v>6599302.093276414</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,7 +1242,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,126 +1257,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>98052068</v>
-      </c>
-      <c r="B7" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Sovtjärnen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>360901.2848806324</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6599302.093276414</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Glava</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-10-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-10-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Jan Rees</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Jan Rees, Per Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
